--- a/school_2/1) walls/vor_spartac_2_walls.xlsx
+++ b/school_2/1) walls/vor_spartac_2_walls.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12504" tabRatio="890" firstSheet="9" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12504" tabRatio="890" firstSheet="4" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="11.n" sheetId="46" r:id="rId1"/>
@@ -13745,7 +13745,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -14004,7 +14004,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -14340,7 +14340,7 @@
     <col min="2" max="2" width="37.88671875" style="267" customWidth="1"/>
     <col min="3" max="3" width="28.88671875" style="267" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="267" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="267" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="267" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="267"/>
   </cols>
   <sheetData>
@@ -14353,7 +14353,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -15642,7 +15642,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -16452,9 +16452,9 @@
   <cols>
     <col min="1" max="1" width="8.6640625" style="267" customWidth="1"/>
     <col min="2" max="2" width="37.88671875" style="267" customWidth="1"/>
-    <col min="3" max="3" width="28.88671875" style="267" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" style="267" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="267" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" style="267" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" style="267" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="267"/>
   </cols>
   <sheetData>
@@ -16467,7 +16467,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -17560,7 +17560,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -17792,7 +17792,7 @@
     <col min="2" max="2" width="37.88671875" style="267" customWidth="1"/>
     <col min="3" max="3" width="26.77734375" style="267" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="267" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="267" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="267" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="267"/>
   </cols>
   <sheetData>
@@ -17805,7 +17805,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -18351,7 +18351,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
@@ -19043,7 +19043,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>72</v>
+        <v>71.2</v>
       </c>
       <c r="T6" s="205">
         <f ca="1">ROUND(
@@ -19053,7 +19053,7 @@
       </c>
       <c r="U6" s="205">
         <f ca="1">SUM(S6:T6)</f>
-        <v>124</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19116,17 +19116,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="T7" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>61.8</v>
+        <v>60.5</v>
       </c>
       <c r="U7" s="205">
         <f t="shared" ref="U7" ca="1" si="0">SUM(S7:T7)</f>
-        <v>114.4</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19195,11 +19195,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>169.9</v>
+        <v>166.5</v>
       </c>
       <c r="U8" s="205">
         <f t="shared" ref="U8:U71" ca="1" si="1">SUM(S8:T8)</f>
-        <v>311.8</v>
+        <v>308.39999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -19262,17 +19262,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="T9" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
       <c r="U9" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>111.8</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19335,17 +19335,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="T10" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>40.1</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="U10" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>63.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19414,11 +19414,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
       <c r="U11" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>65.099999999999994</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19627,7 +19627,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>34.799999999999997</v>
+        <v>35.5</v>
       </c>
       <c r="T14" s="205">
         <f ca="1">ROUND(
@@ -19637,7 +19637,7 @@
       </c>
       <c r="U14" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -19700,17 +19700,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="T15" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>78.400000000000006</v>
+        <v>79.2</v>
       </c>
       <c r="U15" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>89.100000000000009</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -19779,11 +19779,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>32</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="U16" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>32</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19852,11 +19852,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>87.5</v>
+        <v>89.3</v>
       </c>
       <c r="U17" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>112.6</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -19992,17 +19992,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.9</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="T19" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="U19" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>114.1</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -20071,11 +20071,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>82.4</v>
+        <v>84.1</v>
       </c>
       <c r="U20" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>116.4</v>
+        <v>118.1</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -20138,17 +20138,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="T21" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>59.7</v>
+        <v>60.3</v>
       </c>
       <c r="U21" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>111.80000000000001</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -20211,17 +20211,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>173.2</v>
+        <v>171.4</v>
       </c>
       <c r="T22" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>187.3</v>
+        <v>185.4</v>
       </c>
       <c r="U22" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>360.5</v>
+        <v>356.8</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -20357,17 +20357,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>101.3</v>
+        <v>100.3</v>
       </c>
       <c r="T24" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="U24" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>115.8</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -20430,7 +20430,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>16.100000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="T25" s="205">
         <f ca="1">ROUND(
@@ -20440,7 +20440,7 @@
       </c>
       <c r="U25" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -20503,17 +20503,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="T26" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="U26" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -20576,17 +20576,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>195.9</v>
+        <v>193.9</v>
       </c>
       <c r="T27" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>319.2</v>
+        <v>322.39999999999998</v>
       </c>
       <c r="U27" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>515.1</v>
+        <v>516.29999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -20649,17 +20649,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>76</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="T28" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="U28" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>90.4</v>
+        <v>91.699999999999989</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -20722,7 +20722,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>87.1</v>
+        <v>88</v>
       </c>
       <c r="T29" s="205">
         <f ca="1">ROUND(
@@ -20732,7 +20732,7 @@
       </c>
       <c r="U29" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>87.1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -20795,7 +20795,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>35.5</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="T30" s="205">
         <f ca="1">ROUND(
@@ -20805,7 +20805,7 @@
       </c>
       <c r="U30" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>86.4</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -20874,11 +20874,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>55.2</v>
+        <v>55.7</v>
       </c>
       <c r="U31" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>58.900000000000006</v>
+        <v>59.400000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -21093,11 +21093,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>38.700000000000003</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="U34" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>42.1</v>
+        <v>41.699999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -21166,11 +21166,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>69.2</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="U35" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>81.600000000000009</v>
+        <v>82.300000000000011</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -21239,11 +21239,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>67.400000000000006</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="U36" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>73.600000000000009</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -21306,17 +21306,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="T37" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>68.5</v>
+        <v>69.2</v>
       </c>
       <c r="U37" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21379,17 +21379,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="T38" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>103.5</v>
+        <v>105.6</v>
       </c>
       <c r="U38" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>109.6</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -21458,11 +21458,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
       <c r="U39" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -21531,11 +21531,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>35.6</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="U40" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>38.700000000000003</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21598,17 +21598,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.299999999999997</v>
+        <v>40.1</v>
       </c>
       <c r="T41" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>89</v>
+        <v>90.9</v>
       </c>
       <c r="U41" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>128.30000000000001</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21744,7 +21744,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="T43" s="205">
         <f ca="1">ROUND(
@@ -21754,7 +21754,7 @@
       </c>
       <c r="U43" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21817,7 +21817,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>48.2</v>
+        <v>49.2</v>
       </c>
       <c r="T44" s="205">
         <f ca="1">ROUND(
@@ -21827,7 +21827,7 @@
       </c>
       <c r="U44" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>104.6</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21890,7 +21890,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>70.900000000000006</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="T45" s="205">
         <f ca="1">ROUND(
@@ -21900,7 +21900,7 @@
       </c>
       <c r="U45" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>107.2</v>
+        <v>107.89999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -21963,17 +21963,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>74.599999999999994</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="T46" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>36.1</v>
+        <v>36.4</v>
       </c>
       <c r="U46" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>110.69999999999999</v>
+        <v>110.30000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="105.6" x14ac:dyDescent="0.3">
@@ -22036,17 +22036,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="T47" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>149.69999999999999</v>
+        <v>151.30000000000001</v>
       </c>
       <c r="U47" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>177.89999999999998</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -22115,11 +22115,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="U48" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -22182,7 +22182,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>106.1</v>
+        <v>107.2</v>
       </c>
       <c r="T49" s="205">
         <f ca="1">ROUND(
@@ -22192,7 +22192,7 @@
       </c>
       <c r="U49" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>106.1</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -22261,11 +22261,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>149.6</v>
+        <v>152.69999999999999</v>
       </c>
       <c r="U50" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>272.60000000000002</v>
+        <v>275.7</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -22328,17 +22328,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>149.6</v>
+        <v>151.1</v>
       </c>
       <c r="T51" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>206.2</v>
+        <v>210.5</v>
       </c>
       <c r="U51" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>355.79999999999995</v>
+        <v>361.6</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -22401,7 +22401,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="T52" s="205">
         <f ca="1">ROUND(
@@ -22411,7 +22411,7 @@
       </c>
       <c r="U52" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -22547,17 +22547,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>160.30000000000001</v>
+        <v>157</v>
       </c>
       <c r="T54" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>105.4</v>
+        <v>104.3</v>
       </c>
       <c r="U54" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>265.70000000000005</v>
+        <v>261.3</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -22620,7 +22620,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>45.1</v>
+        <v>44.6</v>
       </c>
       <c r="T55" s="205">
         <f ca="1">ROUND(
@@ -22630,7 +22630,7 @@
       </c>
       <c r="U55" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -22693,17 +22693,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="T56" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>69</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="U56" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>84.3</v>
+        <v>83.1</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -22772,11 +22772,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="U57" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -22845,11 +22845,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>33</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="U58" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>34</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -22912,13 +22912,13 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>38.799999999999997</v>
+        <v>38.4</v>
       </c>
       <c r="T59" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.1</v>
+        <v>39.5</v>
       </c>
       <c r="U59" s="205">
         <f t="shared" ca="1" si="1"/>
@@ -22985,17 +22985,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>34.799999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="T60" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="U60" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>47.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23058,7 +23058,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>105.1</v>
+        <v>106.2</v>
       </c>
       <c r="T61" s="205">
         <f ca="1">ROUND(
@@ -23068,7 +23068,7 @@
       </c>
       <c r="U61" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>105.1</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23131,17 +23131,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="T62" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="U62" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>63.8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23210,11 +23210,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>107.4</v>
+        <v>108.5</v>
       </c>
       <c r="U63" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>250.5</v>
+        <v>251.6</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -23283,11 +23283,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="U64" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23356,11 +23356,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>69.2</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="U65" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>91.800000000000011</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23429,11 +23429,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>153.6</v>
+        <v>152</v>
       </c>
       <c r="U66" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>217.39999999999998</v>
+        <v>215.8</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23496,17 +23496,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>112.5</v>
+        <v>111.4</v>
       </c>
       <c r="T67" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>160.5</v>
+        <v>163.80000000000001</v>
       </c>
       <c r="U67" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>273</v>
+        <v>275.20000000000005</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23569,7 +23569,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>84.8</v>
+        <v>83.1</v>
       </c>
       <c r="T68" s="205">
         <f ca="1">ROUND(
@@ -23579,7 +23579,7 @@
       </c>
       <c r="U68" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>84.8</v>
+        <v>83.1</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23721,11 +23721,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>28.9</v>
+        <v>29.2</v>
       </c>
       <c r="U70" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>30.599999999999998</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="71" spans="1:21" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -23794,11 +23794,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>91.8</v>
+        <v>93.7</v>
       </c>
       <c r="U71" s="205">
         <f t="shared" ca="1" si="1"/>
-        <v>161.39999999999998</v>
+        <v>163.30000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23861,7 +23861,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>57</v>
+        <v>57.6</v>
       </c>
       <c r="T72" s="205">
         <f ca="1">ROUND(
@@ -23871,7 +23871,7 @@
       </c>
       <c r="U72" s="205">
         <f t="shared" ref="U72:U135" ca="1" si="2">SUM(S72:T72)</f>
-        <v>236.3</v>
+        <v>236.9</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -23934,17 +23934,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="T73" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>159.1</v>
+        <v>157.5</v>
       </c>
       <c r="U73" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -24007,17 +24007,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>8.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="T74" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="U74" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>14.2</v>
+        <v>14.399999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24080,17 +24080,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>32.6</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="T75" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="U75" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>55.8</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="79.2" x14ac:dyDescent="0.3">
@@ -24153,17 +24153,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="T76" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>184</v>
+        <v>185.9</v>
       </c>
       <c r="U76" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>240</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24232,11 +24232,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
       <c r="U77" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>126.3</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24305,11 +24305,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>61</v>
+        <v>59.8</v>
       </c>
       <c r="U78" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>111.4</v>
+        <v>110.19999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24372,17 +24372,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="T79" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>71.900000000000006</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="U79" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>135.4</v>
+        <v>134.60000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24445,7 +24445,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>186.2</v>
+        <v>188.1</v>
       </c>
       <c r="T80" s="205">
         <f ca="1">ROUND(
@@ -24455,7 +24455,7 @@
       </c>
       <c r="U80" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>351.79999999999995</v>
+        <v>353.7</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24524,11 +24524,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>64.900000000000006</v>
+        <v>65.5</v>
       </c>
       <c r="U81" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>71.800000000000011</v>
+        <v>72.400000000000006</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24591,7 +24591,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>101.7</v>
+        <v>99.6</v>
       </c>
       <c r="T82" s="205">
         <f ca="1">ROUND(
@@ -24601,7 +24601,7 @@
       </c>
       <c r="U82" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>101.7</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24664,17 +24664,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="T83" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>17</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="U83" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -24810,7 +24810,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="T85" s="205">
         <f ca="1">ROUND(
@@ -24820,7 +24820,7 @@
       </c>
       <c r="U85" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>89.8</v>
+        <v>89.899999999999991</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24883,17 +24883,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="T86" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>117.8</v>
+        <v>116.6</v>
       </c>
       <c r="U86" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>161.69999999999999</v>
+        <v>161</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -24962,11 +24962,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>99.5</v>
+        <v>100.5</v>
       </c>
       <c r="U87" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>141.80000000000001</v>
+        <v>142.80000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -25035,11 +25035,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>198.9</v>
+        <v>196.9</v>
       </c>
       <c r="U88" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>350.5</v>
+        <v>348.5</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25108,11 +25108,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>83.5</v>
+        <v>82.6</v>
       </c>
       <c r="U89" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>117.6</v>
+        <v>116.69999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25248,17 +25248,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="T91" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>51.2</v>
+        <v>51.7</v>
       </c>
       <c r="U91" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>76.599999999999994</v>
+        <v>77.400000000000006</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25321,7 +25321,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>100.3</v>
+        <v>99.2</v>
       </c>
       <c r="T92" s="205">
         <f ca="1">ROUND(
@@ -25331,7 +25331,7 @@
       </c>
       <c r="U92" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>114.6</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -25400,11 +25400,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>27.7</v>
+        <v>28.3</v>
       </c>
       <c r="U93" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -25540,7 +25540,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.5</v>
+        <v>39.1</v>
       </c>
       <c r="T95" s="205">
         <f ca="1">ROUND(
@@ -25550,7 +25550,7 @@
       </c>
       <c r="U95" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>292.60000000000002</v>
+        <v>292.2</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25619,11 +25619,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="U96" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>88.5</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="97" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25686,7 +25686,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="T97" s="205">
         <f ca="1">ROUND(
@@ -25696,7 +25696,7 @@
       </c>
       <c r="U97" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>76.899999999999991</v>
+        <v>77.099999999999994</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25759,7 +25759,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>53.2</v>
+        <v>53.7</v>
       </c>
       <c r="T98" s="205">
         <f ca="1">ROUND(
@@ -25769,7 +25769,7 @@
       </c>
       <c r="U98" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>133.9</v>
+        <v>134.4</v>
       </c>
     </row>
     <row r="99" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -25905,7 +25905,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>88</v>
+        <v>86.2</v>
       </c>
       <c r="T100" s="205">
         <f ca="1">ROUND(
@@ -25915,7 +25915,7 @@
       </c>
       <c r="U100" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>88</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="101" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -26124,17 +26124,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="T103" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>95.2</v>
+        <v>96.1</v>
       </c>
       <c r="U103" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>140.5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26203,11 +26203,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>77.099999999999994</v>
+        <v>76.3</v>
       </c>
       <c r="U104" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>109</v>
+        <v>108.19999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -26270,17 +26270,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T105" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="U105" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>31.1</v>
+        <v>30.799999999999997</v>
       </c>
     </row>
     <row r="106" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26349,11 +26349,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>63.5</v>
+        <v>64.2</v>
       </c>
       <c r="U106" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>113.6</v>
+        <v>114.30000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26422,11 +26422,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>35.4</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="U107" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>108</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="108" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26489,17 +26489,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="T108" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>37.299999999999997</v>
+        <v>38.1</v>
       </c>
       <c r="U108" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>111.3</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="109" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26708,17 +26708,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="T111" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>61.6</v>
+        <v>61</v>
       </c>
       <c r="U111" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>112.80000000000001</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26781,7 +26781,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="T112" s="205">
         <f ca="1">ROUND(
@@ -26791,7 +26791,7 @@
       </c>
       <c r="U112" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>114.4</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="113" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26854,17 +26854,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>89.3</v>
+        <v>90.2</v>
       </c>
       <c r="T113" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>148.5</v>
+        <v>150</v>
       </c>
       <c r="U113" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>237.8</v>
+        <v>240.2</v>
       </c>
     </row>
     <row r="114" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -26927,17 +26927,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>89.4</v>
+        <v>90.3</v>
       </c>
       <c r="T114" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>166.4</v>
+        <v>163.1</v>
       </c>
       <c r="U114" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>255.8</v>
+        <v>253.39999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27000,7 +27000,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="T115" s="205">
         <f ca="1">ROUND(
@@ -27010,7 +27010,7 @@
       </c>
       <c r="U115" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>69.900000000000006</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27073,17 +27073,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>76.7</v>
+        <v>75.2</v>
       </c>
       <c r="T116" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>97.2</v>
+        <v>96.2</v>
       </c>
       <c r="U116" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>173.9</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="117" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27225,11 +27225,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>68.400000000000006</v>
+        <v>67.7</v>
       </c>
       <c r="U118" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>84.100000000000009</v>
+        <v>83.4</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -27298,11 +27298,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>39.1</v>
+        <v>39.5</v>
       </c>
       <c r="U119" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>77.099999999999994</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="120" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -27365,7 +27365,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T120" s="205">
         <f ca="1">ROUND(
@@ -27375,7 +27375,7 @@
       </c>
       <c r="U120" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="121" spans="1:21" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -27511,17 +27511,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="T122" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>17</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="U122" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="123" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27584,7 +27584,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>108.3</v>
+        <v>107.2</v>
       </c>
       <c r="T123" s="205">
         <f ca="1">ROUND(
@@ -27594,7 +27594,7 @@
       </c>
       <c r="U123" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>108.3</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="124" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27657,17 +27657,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>37.700000000000003</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="T124" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>131.69999999999999</v>
+        <v>133.1</v>
       </c>
       <c r="U124" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>169.39999999999998</v>
+        <v>170.39999999999998</v>
       </c>
     </row>
     <row r="125" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27730,17 +27730,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="T125" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>78.599999999999994</v>
+        <v>77.8</v>
       </c>
       <c r="U125" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>96.899999999999991</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="126" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27803,17 +27803,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>100.7</v>
+        <v>102.8</v>
       </c>
       <c r="T126" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>118.7</v>
+        <v>116.3</v>
       </c>
       <c r="U126" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>219.4</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="127" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27876,7 +27876,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>104.2</v>
+        <v>106.3</v>
       </c>
       <c r="T127" s="205">
         <f ca="1">ROUND(
@@ -27886,7 +27886,7 @@
       </c>
       <c r="U127" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>303.39999999999998</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="128" spans="1:21" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -27949,7 +27949,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>86.4</v>
+        <v>88.2</v>
       </c>
       <c r="T128" s="205">
         <f ca="1">ROUND(
@@ -27959,7 +27959,7 @@
       </c>
       <c r="U128" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>86.4</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="129" spans="1:24" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -28022,17 +28022,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>95.2</v>
+        <v>97.1</v>
       </c>
       <c r="T129" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>127.7</v>
+        <v>126.4</v>
       </c>
       <c r="U129" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>222.9</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="130" spans="1:24" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -28095,17 +28095,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>58.2</v>
+        <v>58.8</v>
       </c>
       <c r="T130" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>105.2</v>
+        <v>103.1</v>
       </c>
       <c r="U130" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>163.4</v>
+        <v>161.89999999999998</v>
       </c>
     </row>
     <row r="131" spans="1:24" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -28241,17 +28241,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="T132" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="U132" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>35.200000000000003</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="133" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28314,17 +28314,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>37.700000000000003</v>
+        <v>38.1</v>
       </c>
       <c r="T133" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>94.7</v>
+        <v>96.6</v>
       </c>
       <c r="U133" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>132.4</v>
+        <v>134.69999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:24" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -28387,17 +28387,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="T134" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>38.6</v>
+        <v>39</v>
       </c>
       <c r="U134" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="135" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28460,7 +28460,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="T135" s="205">
         <f ca="1">ROUND(
@@ -28470,7 +28470,7 @@
       </c>
       <c r="U135" s="205">
         <f t="shared" ca="1" si="2"/>
-        <v>42.6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28539,11 +28539,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>43.1</v>
+        <v>44</v>
       </c>
       <c r="U136" s="205">
         <f t="shared" ref="U136:U142" ca="1" si="3">SUM(S136:T136)</f>
-        <v>47.800000000000004</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="137" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28612,11 +28612,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>34.4</v>
+        <v>35.1</v>
       </c>
       <c r="U137" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>45.099999999999994</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="138" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28679,17 +28679,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>53.7</v>
+        <v>52.6</v>
       </c>
       <c r="T138" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>116.9</v>
+        <v>115.7</v>
       </c>
       <c r="U138" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>170.60000000000002</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="139" spans="1:24" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -28758,11 +28758,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>57.6</v>
+        <v>57</v>
       </c>
       <c r="U139" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>59.2</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="140" spans="1:24" ht="92.4" hidden="1" x14ac:dyDescent="0.3">
@@ -28825,17 +28825,17 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>8.1999999999999993</v>
+        <v>8.1</v>
       </c>
       <c r="T140" s="205">
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="U140" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>14.299999999999999</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="141" spans="1:24" ht="105.6" hidden="1" x14ac:dyDescent="0.3">
@@ -28904,11 +28904,11 @@
         <f ca="1">ROUND(
     SUM(Таблица3[[#This Row],[Столбец6]:[Столбец13]]) * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>155</v>
+        <v>153.5</v>
       </c>
       <c r="U141" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>180</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="142" spans="1:24" ht="79.2" hidden="1" x14ac:dyDescent="0.3">
@@ -28971,7 +28971,7 @@
         <f ca="1">ROUND(
    Таблица3[[#This Row],[Столбец4]] * RANDBETWEEN(97,99)/100,
 1)</f>
-        <v>32.200000000000003</v>
+        <v>31.9</v>
       </c>
       <c r="T142" s="205">
         <f ca="1">ROUND(
@@ -28981,7 +28981,7 @@
       </c>
       <c r="U142" s="205">
         <f t="shared" ca="1" si="3"/>
-        <v>55.400000000000006</v>
+        <v>55.099999999999994</v>
       </c>
     </row>
     <row r="143" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
@@ -29011,23 +29011,23 @@
       <c r="R143" s="255"/>
       <c r="S143" s="255">
         <f ca="1">SUBTOTAL(109,Таблица1[по ж/б поверхностям])</f>
-        <v>768.60000000000014</v>
+        <v>771.1</v>
       </c>
       <c r="T143" s="255">
         <f ca="1">SUM(Таблица1[[ по газобетонному блоку и ПГП]])</f>
-        <v>9935.5000000000073</v>
+        <v>9944.8000000000047</v>
       </c>
       <c r="U143" s="255">
         <f ca="1">SUBTOTAL(109,Таблица1[Итог])</f>
-        <v>1686.8</v>
+        <v>1697.3000000000002</v>
       </c>
       <c r="W143" s="189">
         <f ca="1">Таблица1[[#Totals],[по ж/б поверхностям]]/Таблица3[[#Totals],[Столбец4]]*100</f>
-        <v>10.868520037331377</v>
+        <v>10.903871715829071</v>
       </c>
       <c r="X143" s="189">
         <f ca="1">Таблица1[[#Totals],[ по газобетонному блоку и ПГП]]/Таблица3[[#Totals],[Столбец8]]*100</f>
-        <v>97.983234714004027</v>
+        <v>98.07495069033537</v>
       </c>
     </row>
     <row r="148" spans="1:18" x14ac:dyDescent="0.3">
@@ -57815,7 +57815,7 @@
       <c r="D1" s="265"/>
       <c r="E1" s="266"/>
     </row>
-    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="263" t="s">
         <v>0</v>
       </c>
